--- a/output/lettera25.xlsx
+++ b/output/lettera25.xlsx
@@ -730,7 +730,7 @@
     <t>presso</t>
   </si>
   <si>
-    <t>⁄4</t>
+    <t>⁄</t>
   </si>
   <si>
     <t>quasi</t>
